--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040758</v>
+        <v>120040843</v>
       </c>
       <c r="B3" t="n">
-        <v>100171</v>
+        <v>109824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576227</v>
+        <v>576151</v>
       </c>
       <c r="R3" t="n">
-        <v>6422890</v>
+        <v>6422893</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040843</v>
+        <v>120040758</v>
       </c>
       <c r="B4" t="n">
-        <v>109824</v>
+        <v>100171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576151</v>
+        <v>576227</v>
       </c>
       <c r="R4" t="n">
-        <v>6422893</v>
+        <v>6422890</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040790</v>
+        <v>120040843</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>109824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576153</v>
+        <v>576151</v>
       </c>
       <c r="R2" t="n">
-        <v>6422892</v>
+        <v>6422893</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040843</v>
+        <v>120040790</v>
       </c>
       <c r="B3" t="n">
-        <v>109824</v>
+        <v>100171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576151</v>
+        <v>576153</v>
       </c>
       <c r="R3" t="n">
-        <v>6422893</v>
+        <v>6422892</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040843</v>
+        <v>120040790</v>
       </c>
       <c r="B2" t="n">
-        <v>109824</v>
+        <v>100171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576151</v>
+        <v>576153</v>
       </c>
       <c r="R2" t="n">
-        <v>6422893</v>
+        <v>6422892</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040790</v>
+        <v>120040843</v>
       </c>
       <c r="B3" t="n">
-        <v>100171</v>
+        <v>109824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576153</v>
+        <v>576151</v>
       </c>
       <c r="R3" t="n">
-        <v>6422892</v>
+        <v>6422893</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040790</v>
+        <v>120040758</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576153</v>
+        <v>576227</v>
       </c>
       <c r="R2" t="n">
-        <v>6422892</v>
+        <v>6422890</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040843</v>
+        <v>120040790</v>
       </c>
       <c r="B3" t="n">
-        <v>109824</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576151</v>
+        <v>576153</v>
       </c>
       <c r="R3" t="n">
-        <v>6422893</v>
+        <v>6422892</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040758</v>
+        <v>120040843</v>
       </c>
       <c r="B4" t="n">
-        <v>100171</v>
+        <v>109848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576227</v>
+        <v>576151</v>
       </c>
       <c r="R4" t="n">
-        <v>6422890</v>
+        <v>6422893</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040758</v>
+        <v>120040790</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576227</v>
+        <v>576153</v>
       </c>
       <c r="R2" t="n">
-        <v>6422890</v>
+        <v>6422892</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -783,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040790</v>
+        <v>120040843</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
+        <v>109848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576153</v>
+        <v>576151</v>
       </c>
       <c r="R3" t="n">
-        <v>6422892</v>
+        <v>6422893</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -898,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040843</v>
+        <v>120040758</v>
       </c>
       <c r="B4" t="n">
-        <v>109848</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576151</v>
+        <v>576227</v>
       </c>
       <c r="R4" t="n">
-        <v>6422893</v>
+        <v>6422890</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040790</v>
+        <v>120040843</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>109848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576153</v>
+        <v>576151</v>
       </c>
       <c r="R2" t="n">
-        <v>6422892</v>
+        <v>6422893</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -783,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040843</v>
+        <v>120040758</v>
       </c>
       <c r="B3" t="n">
-        <v>109848</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576151</v>
+        <v>576227</v>
       </c>
       <c r="R3" t="n">
-        <v>6422893</v>
+        <v>6422890</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -898,14 +898,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040758</v>
+        <v>120040790</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576227</v>
+        <v>576153</v>
       </c>
       <c r="R4" t="n">
-        <v>6422890</v>
+        <v>6422892</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040843</v>
+        <v>120040790</v>
       </c>
       <c r="B2" t="n">
-        <v>109848</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576151</v>
+        <v>576153</v>
       </c>
       <c r="R2" t="n">
-        <v>6422893</v>
+        <v>6422892</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -783,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040758</v>
+        <v>120040843</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
+        <v>109848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576227</v>
+        <v>576151</v>
       </c>
       <c r="R3" t="n">
-        <v>6422890</v>
+        <v>6422893</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -898,14 +898,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040790</v>
+        <v>120040758</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576153</v>
+        <v>576227</v>
       </c>
       <c r="R4" t="n">
-        <v>6422892</v>
+        <v>6422890</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040790</v>
+        <v>120040758</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576153</v>
+        <v>576227</v>
       </c>
       <c r="R2" t="n">
-        <v>6422892</v>
+        <v>6422890</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040843</v>
+        <v>120040790</v>
       </c>
       <c r="B3" t="n">
-        <v>109848</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576151</v>
+        <v>576153</v>
       </c>
       <c r="R3" t="n">
-        <v>6422893</v>
+        <v>6422892</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040758</v>
+        <v>120040843</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>109848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576227</v>
+        <v>576151</v>
       </c>
       <c r="R4" t="n">
-        <v>6422890</v>
+        <v>6422893</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040790</v>
+        <v>120040843</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
+        <v>109848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576153</v>
+        <v>576151</v>
       </c>
       <c r="R3" t="n">
-        <v>6422892</v>
+        <v>6422893</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040843</v>
+        <v>120040790</v>
       </c>
       <c r="B4" t="n">
-        <v>109848</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +921,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576151</v>
+        <v>576153</v>
       </c>
       <c r="R4" t="n">
-        <v>6422893</v>
+        <v>6422892</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 40331-2024 artfynd.xlsx
+++ b/artfynd/A 40331-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040790</v>
+        <v>120040843</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576153</v>
+        <v>576151</v>
       </c>
       <c r="R2" t="n">
-        <v>6422892</v>
+        <v>6422893</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -790,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040758</v>
+        <v>120040873</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,31 +796,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576227</v>
+        <v>576149</v>
       </c>
       <c r="R3" t="n">
-        <v>6422890</v>
+        <v>6422887</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -905,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040843</v>
+        <v>120040758</v>
       </c>
       <c r="B4" t="n">
-        <v>109848</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +930,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576151</v>
+        <v>576227</v>
       </c>
       <c r="R4" t="n">
-        <v>6422893</v>
+        <v>6422890</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1017,6 +1002,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120040790</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>sothem_A40331, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576153</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6422892</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
